--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseEndReceiveTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseEndReceiveTemplate.xlsx
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -47,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -58,6 +72,21 @@
         <scheme val="minor"/>
       </rPr>
       <t>SKU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>结束交货原因</t>
     </r>
   </si>
 </sst>
@@ -999,19 +1028,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
